--- a/backend/data/financials_by_company/0845.HK.xlsx
+++ b/backend/data/financials_by_company/0845.HK.xlsx
@@ -662,59 +662,57 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>7351653.254321</v>
+        <v>-157666245</v>
       </c>
       <c r="C2" t="n">
-        <v>0.132412</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-1329124000</v>
+        <v>-1859089000</v>
       </c>
       <c r="E2" t="n">
-        <v>55521000</v>
+        <v>-955553000</v>
       </c>
       <c r="F2" t="n">
-        <v>55521000</v>
+        <v>-955553000</v>
       </c>
       <c r="G2" t="n">
-        <v>-2949153000</v>
+        <v>-5150032000</v>
       </c>
       <c r="H2" t="n">
-        <v>21329000</v>
+        <v>15709000</v>
       </c>
       <c r="I2" t="n">
-        <v>1806299000</v>
+        <v>4408688000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1273603000</v>
+        <v>-2814642000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1294932000</v>
+        <v>-2830351000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2101961000</v>
+        <v>-2073909000</v>
       </c>
       <c r="M2" t="n">
-        <v>2104349000</v>
+        <v>2112067000</v>
       </c>
       <c r="N2" t="n">
-        <v>2388000</v>
+        <v>38158000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2997322346.745679</v>
+        <v>-4352145245</v>
       </c>
       <c r="P2" t="n">
-        <v>-2949153000</v>
+        <v>-5150032000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2137188000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8555000</v>
-      </c>
+        <v>5066965000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>7792646000</v>
       </c>
@@ -722,86 +720,86 @@
         <v>7792646000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.38</v>
+        <v>-0.66</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.38</v>
+        <v>-0.66</v>
       </c>
       <c r="W2" t="n">
-        <v>-2949153000</v>
+        <v>-5150032000</v>
       </c>
       <c r="X2" t="n">
-        <v>-2949153000</v>
+        <v>-5150032000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2949153000</v>
+        <v>-5150032000</v>
       </c>
       <c r="AA2" t="n">
-        <v>22000</v>
+        <v>13817000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2949175000</v>
+        <v>-5163849000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2949175000</v>
+        <v>-5163849000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-450106000</v>
+        <v>221431000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3399281000</v>
+        <v>-4942418000</v>
       </c>
       <c r="AF2" t="n">
-        <v>65867000</v>
+        <v>35215000</v>
       </c>
       <c r="AG2" t="n">
-        <v>55521000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-55521000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>-955553000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>955553000</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>-2101961000</v>
+        <v>-2073909000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2104349000</v>
+        <v>2112067000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2388000</v>
+        <v>38158000</v>
       </c>
       <c r="AM2" t="n">
-        <v>502468000</v>
+        <v>-1749383000</v>
       </c>
       <c r="AN2" t="n">
-        <v>330889000</v>
+        <v>658277000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-15359000</v>
+        <v>56879000</v>
       </c>
       <c r="AP2" t="n">
-        <v>346248000</v>
+        <v>601398000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>105043000</v>
+        <v>175019000</v>
       </c>
       <c r="AR2" t="n">
-        <v>241205000</v>
+        <v>426379000</v>
       </c>
       <c r="AS2" t="n">
-        <v>833357000</v>
+        <v>-1091106000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1806299000</v>
+        <v>4408688000</v>
       </c>
       <c r="AU2" t="n">
-        <v>2639656000</v>
+        <v>3317582000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2639656000</v>
+        <v>3317582000</v>
       </c>
     </row>
     <row r="3">
@@ -950,57 +948,59 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-157666245</v>
+        <v>7351653.254321</v>
       </c>
       <c r="C4" t="n">
-        <v>0.165</v>
+        <v>0.132412</v>
       </c>
       <c r="D4" t="n">
-        <v>-1859089000</v>
+        <v>-1329124000</v>
       </c>
       <c r="E4" t="n">
-        <v>-955553000</v>
+        <v>55521000</v>
       </c>
       <c r="F4" t="n">
-        <v>-955553000</v>
+        <v>55521000</v>
       </c>
       <c r="G4" t="n">
-        <v>-5150032000</v>
+        <v>-2949153000</v>
       </c>
       <c r="H4" t="n">
-        <v>15709000</v>
+        <v>21329000</v>
       </c>
       <c r="I4" t="n">
-        <v>4408688000</v>
+        <v>1806299000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2814642000</v>
+        <v>-1273603000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2830351000</v>
+        <v>-1294932000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2073909000</v>
+        <v>-2101961000</v>
       </c>
       <c r="M4" t="n">
-        <v>2112067000</v>
+        <v>2104349000</v>
       </c>
       <c r="N4" t="n">
-        <v>38158000</v>
+        <v>2388000</v>
       </c>
       <c r="O4" t="n">
-        <v>-4352145245</v>
+        <v>-2997322346.745679</v>
       </c>
       <c r="P4" t="n">
-        <v>-5150032000</v>
+        <v>-2949153000</v>
       </c>
       <c r="Q4" t="n">
-        <v>5066965000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>2137188000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8555000</v>
+      </c>
       <c r="S4" t="n">
         <v>7792646000</v>
       </c>
@@ -1008,86 +1008,86 @@
         <v>7792646000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.66</v>
+        <v>-0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.66</v>
+        <v>-0.38</v>
       </c>
       <c r="W4" t="n">
-        <v>-5150032000</v>
+        <v>-2949153000</v>
       </c>
       <c r="X4" t="n">
-        <v>-5150032000</v>
+        <v>-2949153000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-5150032000</v>
+        <v>-2949153000</v>
       </c>
       <c r="AA4" t="n">
-        <v>13817000</v>
+        <v>22000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-5163849000</v>
+        <v>-2949175000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5163849000</v>
+        <v>-2949175000</v>
       </c>
       <c r="AD4" t="n">
-        <v>221431000</v>
+        <v>-450106000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-4942418000</v>
+        <v>-3399281000</v>
       </c>
       <c r="AF4" t="n">
-        <v>35215000</v>
+        <v>65867000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-955553000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
-        <v>955553000</v>
-      </c>
+        <v>55521000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-55521000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>-2073909000</v>
+        <v>-2101961000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2112067000</v>
+        <v>2104349000</v>
       </c>
       <c r="AL4" t="n">
-        <v>38158000</v>
+        <v>2388000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1749383000</v>
+        <v>502468000</v>
       </c>
       <c r="AN4" t="n">
-        <v>658277000</v>
+        <v>330889000</v>
       </c>
       <c r="AO4" t="n">
-        <v>56879000</v>
+        <v>-15359000</v>
       </c>
       <c r="AP4" t="n">
-        <v>601398000</v>
+        <v>346248000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>175019000</v>
+        <v>105043000</v>
       </c>
       <c r="AR4" t="n">
-        <v>426379000</v>
+        <v>241205000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1091106000</v>
+        <v>833357000</v>
       </c>
       <c r="AT4" t="n">
-        <v>4408688000</v>
+        <v>1806299000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3317582000</v>
+        <v>2639656000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3317582000</v>
+        <v>2639656000</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>7792645623</v>
@@ -1422,40 +1422,40 @@
         <v>7792645623</v>
       </c>
       <c r="D2" t="n">
-        <v>22611043000</v>
+        <v>19892363000</v>
       </c>
       <c r="E2" t="n">
-        <v>22664933000</v>
+        <v>20084441000</v>
       </c>
       <c r="F2" t="n">
-        <v>-2958182000</v>
+        <v>288326000</v>
       </c>
       <c r="G2" t="n">
-        <v>19707005000</v>
+        <v>20374131000</v>
       </c>
       <c r="H2" t="n">
-        <v>-24189827000</v>
+        <v>-23184980000</v>
       </c>
       <c r="I2" t="n">
-        <v>-2958182000</v>
+        <v>288326000</v>
       </c>
       <c r="J2" t="n">
-        <v>1546000</v>
+        <v>436000</v>
       </c>
       <c r="K2" t="n">
-        <v>-2956382000</v>
+        <v>290126000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2956382000</v>
+        <v>290126000</v>
       </c>
       <c r="M2" t="n">
-        <v>-2822000000</v>
+        <v>424641000</v>
       </c>
       <c r="N2" t="n">
-        <v>134382000</v>
+        <v>134515000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2956382000</v>
+        <v>290126000</v>
       </c>
       <c r="P2" t="n">
         <v>7822982000</v>
@@ -1467,67 +1467,67 @@
         <v>68745000</v>
       </c>
       <c r="S2" t="n">
-        <v>47650088000</v>
+        <v>49464515000</v>
       </c>
       <c r="T2" t="n">
-        <v>2382645000</v>
+        <v>2237180000</v>
       </c>
       <c r="U2" t="n">
-        <v>2382035000</v>
+        <v>2237180000</v>
       </c>
       <c r="V2" t="n">
-        <v>610000</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>610000</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>45267443000</v>
+        <v>47227335000</v>
       </c>
       <c r="Z2" t="n">
-        <v>22664323000</v>
+        <v>20084441000</v>
       </c>
       <c r="AA2" t="n">
-        <v>936000</v>
+        <v>436000</v>
       </c>
       <c r="AB2" t="n">
-        <v>22663387000</v>
+        <v>20084005000</v>
       </c>
       <c r="AC2" t="n">
-        <v>16314541000</v>
+        <v>14991063000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2524704000</v>
+        <v>1951721000</v>
       </c>
       <c r="AE2" t="n">
-        <v>10997387000</v>
+        <v>9176296000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2792450000</v>
+        <v>3863046000</v>
       </c>
       <c r="AG2" t="n">
-        <v>44828088000</v>
+        <v>49889156000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23750472000</v>
+        <v>25846801000</v>
       </c>
       <c r="AI2" t="n">
-        <v>697359000</v>
+        <v>279313000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>349891000</v>
+        <v>882724000</v>
       </c>
       <c r="AK2" t="n">
-        <v>343991000</v>
+        <v>876497000</v>
       </c>
       <c r="AL2" t="n">
-        <v>5900000</v>
+        <v>6227000</v>
       </c>
       <c r="AM2" t="n">
-        <v>22385588000</v>
+        <v>24309410000</v>
       </c>
       <c r="AN2" t="n">
         <v>1800000</v>
@@ -1536,63 +1536,67 @@
         <v>1800000</v>
       </c>
       <c r="AP2" t="n">
-        <v>315834000</v>
+        <v>373554000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-104055000</v>
+        <v>-120798000</v>
       </c>
       <c r="AR2" t="n">
-        <v>419889000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>494352000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>101060000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>95929000</v>
+        <v>99912000</v>
       </c>
       <c r="AU2" t="n">
-        <v>79902000</v>
+        <v>122340000</v>
       </c>
       <c r="AV2" t="n">
-        <v>244058000</v>
+        <v>272100000</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>21077616000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>24042355000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>148000000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>189523000</v>
+        <v>406615000</v>
       </c>
       <c r="BA2" t="n">
-        <v>2517108000</v>
+        <v>2666008000</v>
       </c>
       <c r="BB2" t="n">
-        <v>17357848000</v>
+        <v>19865244000</v>
       </c>
       <c r="BC2" t="n">
-        <v>17357848000</v>
+        <v>19865244000</v>
       </c>
       <c r="BD2" t="n">
-        <v>793502000</v>
+        <v>443024000</v>
       </c>
       <c r="BE2" t="n">
-        <v>167291000</v>
+        <v>469822000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-17291000</v>
+        <v>-5813000</v>
       </c>
       <c r="BG2" t="n">
-        <v>184582000</v>
+        <v>475635000</v>
       </c>
       <c r="BH2" t="n">
-        <v>52344000</v>
+        <v>191642000</v>
       </c>
       <c r="BI2" t="n">
-        <v>52344000</v>
+        <v>191642000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>52344000</v>
+        <v>191642000</v>
       </c>
     </row>
     <row r="3">
@@ -1785,7 +1789,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>7792645623</v>
@@ -1794,40 +1798,40 @@
         <v>7792645623</v>
       </c>
       <c r="D4" t="n">
-        <v>19892363000</v>
+        <v>22611043000</v>
       </c>
       <c r="E4" t="n">
-        <v>20084441000</v>
+        <v>22664933000</v>
       </c>
       <c r="F4" t="n">
-        <v>288326000</v>
+        <v>-2958182000</v>
       </c>
       <c r="G4" t="n">
-        <v>20374131000</v>
+        <v>19707005000</v>
       </c>
       <c r="H4" t="n">
-        <v>-23184980000</v>
+        <v>-24189827000</v>
       </c>
       <c r="I4" t="n">
-        <v>288326000</v>
+        <v>-2958182000</v>
       </c>
       <c r="J4" t="n">
-        <v>436000</v>
+        <v>1546000</v>
       </c>
       <c r="K4" t="n">
-        <v>290126000</v>
+        <v>-2956382000</v>
       </c>
       <c r="L4" t="n">
-        <v>290126000</v>
+        <v>-2956382000</v>
       </c>
       <c r="M4" t="n">
-        <v>424641000</v>
+        <v>-2822000000</v>
       </c>
       <c r="N4" t="n">
-        <v>134515000</v>
+        <v>134382000</v>
       </c>
       <c r="O4" t="n">
-        <v>290126000</v>
+        <v>-2956382000</v>
       </c>
       <c r="P4" t="n">
         <v>7822982000</v>
@@ -1839,67 +1843,67 @@
         <v>68745000</v>
       </c>
       <c r="S4" t="n">
-        <v>49464515000</v>
+        <v>47650088000</v>
       </c>
       <c r="T4" t="n">
-        <v>2237180000</v>
+        <v>2382645000</v>
       </c>
       <c r="U4" t="n">
-        <v>2237180000</v>
+        <v>2382035000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>610000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>610000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>47227335000</v>
+        <v>45267443000</v>
       </c>
       <c r="Z4" t="n">
-        <v>20084441000</v>
+        <v>22664323000</v>
       </c>
       <c r="AA4" t="n">
-        <v>436000</v>
+        <v>936000</v>
       </c>
       <c r="AB4" t="n">
-        <v>20084005000</v>
+        <v>22663387000</v>
       </c>
       <c r="AC4" t="n">
-        <v>14991063000</v>
+        <v>16314541000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1951721000</v>
+        <v>2524704000</v>
       </c>
       <c r="AE4" t="n">
-        <v>9176296000</v>
+        <v>10997387000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3863046000</v>
+        <v>2792450000</v>
       </c>
       <c r="AG4" t="n">
-        <v>49889156000</v>
+        <v>44828088000</v>
       </c>
       <c r="AH4" t="n">
-        <v>25846801000</v>
+        <v>23750472000</v>
       </c>
       <c r="AI4" t="n">
-        <v>279313000</v>
+        <v>697359000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>882724000</v>
+        <v>349891000</v>
       </c>
       <c r="AK4" t="n">
-        <v>876497000</v>
+        <v>343991000</v>
       </c>
       <c r="AL4" t="n">
-        <v>6227000</v>
+        <v>5900000</v>
       </c>
       <c r="AM4" t="n">
-        <v>24309410000</v>
+        <v>22385588000</v>
       </c>
       <c r="AN4" t="n">
         <v>1800000</v>
@@ -1908,67 +1912,63 @@
         <v>1800000</v>
       </c>
       <c r="AP4" t="n">
-        <v>373554000</v>
+        <v>315834000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-120798000</v>
+        <v>-104055000</v>
       </c>
       <c r="AR4" t="n">
-        <v>494352000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>101060000</v>
-      </c>
+        <v>419889000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>99912000</v>
+        <v>95929000</v>
       </c>
       <c r="AU4" t="n">
-        <v>122340000</v>
+        <v>79902000</v>
       </c>
       <c r="AV4" t="n">
-        <v>272100000</v>
+        <v>244058000</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>24042355000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>148000000</v>
-      </c>
+        <v>21077616000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>406615000</v>
+        <v>189523000</v>
       </c>
       <c r="BA4" t="n">
-        <v>2666008000</v>
+        <v>2517108000</v>
       </c>
       <c r="BB4" t="n">
-        <v>19865244000</v>
+        <v>17357848000</v>
       </c>
       <c r="BC4" t="n">
-        <v>19865244000</v>
+        <v>17357848000</v>
       </c>
       <c r="BD4" t="n">
-        <v>443024000</v>
+        <v>793502000</v>
       </c>
       <c r="BE4" t="n">
-        <v>469822000</v>
+        <v>167291000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-5813000</v>
+        <v>-17291000</v>
       </c>
       <c r="BG4" t="n">
-        <v>475635000</v>
+        <v>184582000</v>
       </c>
       <c r="BH4" t="n">
-        <v>191642000</v>
+        <v>52344000</v>
       </c>
       <c r="BI4" t="n">
-        <v>191642000</v>
+        <v>52344000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>191642000</v>
+        <v>52344000</v>
       </c>
     </row>
   </sheetData>
@@ -2194,124 +2194,130 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>365473000</v>
+        <v>-291974000</v>
       </c>
       <c r="C2" t="n">
-        <v>-429914000</v>
+        <v>-5098991000</v>
       </c>
       <c r="D2" t="n">
-        <v>198359000</v>
+        <v>5107604000</v>
       </c>
       <c r="E2" t="n">
-        <v>-510000</v>
+        <v>-957000</v>
       </c>
       <c r="F2" t="n">
-        <v>214647000</v>
+        <v>191642000</v>
       </c>
       <c r="G2" t="n">
-        <v>290859000</v>
+        <v>395543000</v>
       </c>
       <c r="H2" t="n">
-        <v>-5000</v>
+        <v>-11000</v>
       </c>
       <c r="I2" t="n">
-        <v>-76207000</v>
+        <v>-203890000</v>
       </c>
       <c r="J2" t="n">
-        <v>-232714000</v>
+        <v>7282000</v>
       </c>
       <c r="K2" t="n">
-        <v>-231555000</v>
+        <v>8613000</v>
       </c>
       <c r="L2" t="n">
-        <v>-231555000</v>
+        <v>8613000</v>
       </c>
       <c r="M2" t="n">
-        <v>-429914000</v>
+        <v>-5098991000</v>
       </c>
       <c r="N2" t="n">
-        <v>198359000</v>
+        <v>5107604000</v>
       </c>
       <c r="O2" t="n">
-        <v>-209476000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>79845000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>137943000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>2388000</v>
+        <v>38158000</v>
       </c>
       <c r="R2" t="n">
-        <v>-224064000</v>
+        <v>-215299000</v>
       </c>
       <c r="S2" t="n">
-        <v>35722000</v>
+        <v>547996000</v>
       </c>
       <c r="T2" t="n">
-        <v>-259786000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>-763295000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>120000000</v>
+      </c>
       <c r="W2" t="n">
-        <v>-356000</v>
+        <v>-957000</v>
       </c>
       <c r="X2" t="n">
-        <v>154000</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-510000</v>
+        <v>-957000</v>
       </c>
       <c r="Z2" t="n">
-        <v>365983000</v>
+        <v>-291017000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-172390000</v>
+        <v>-91830000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-414504000</v>
+        <v>-2106509000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-366815000</v>
+        <v>2571424000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1240460000</v>
+        <v>2621751000</v>
       </c>
       <c r="AE2" t="n">
-        <v>116482000</v>
+        <v>524024000</v>
       </c>
       <c r="AF2" t="n">
-        <v>872340000</v>
+        <v>-137707000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-115177000</v>
+        <v>-436644000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2101961000</v>
+        <v>2073909000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-15359000</v>
+        <v>56879000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-450106000</v>
+        <v>221431000</v>
       </c>
       <c r="AK2" t="n">
-        <v>21329000</v>
+        <v>15709000</v>
       </c>
       <c r="AL2" t="n">
-        <v>21329000</v>
+        <v>15709000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1457471000</v>
+        <v>213828000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3721000</v>
+        <v>-9025000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-55521000</v>
+        <v>32000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-2949175000</v>
+        <v>-5163849000</v>
       </c>
     </row>
     <row r="3">
@@ -2442,130 +2448,124 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-291974000</v>
+        <v>365473000</v>
       </c>
       <c r="C4" t="n">
-        <v>-5098991000</v>
+        <v>-429914000</v>
       </c>
       <c r="D4" t="n">
-        <v>5107604000</v>
+        <v>198359000</v>
       </c>
       <c r="E4" t="n">
-        <v>-957000</v>
+        <v>-510000</v>
       </c>
       <c r="F4" t="n">
-        <v>191642000</v>
+        <v>214647000</v>
       </c>
       <c r="G4" t="n">
-        <v>395543000</v>
+        <v>290859000</v>
       </c>
       <c r="H4" t="n">
-        <v>-11000</v>
+        <v>-5000</v>
       </c>
       <c r="I4" t="n">
-        <v>-203890000</v>
+        <v>-76207000</v>
       </c>
       <c r="J4" t="n">
-        <v>7282000</v>
+        <v>-232714000</v>
       </c>
       <c r="K4" t="n">
-        <v>8613000</v>
+        <v>-231555000</v>
       </c>
       <c r="L4" t="n">
-        <v>8613000</v>
+        <v>-231555000</v>
       </c>
       <c r="M4" t="n">
-        <v>-5098991000</v>
+        <v>-429914000</v>
       </c>
       <c r="N4" t="n">
-        <v>5107604000</v>
+        <v>198359000</v>
       </c>
       <c r="O4" t="n">
-        <v>79845000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>137943000</v>
-      </c>
+        <v>-209476000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>38158000</v>
+        <v>2388000</v>
       </c>
       <c r="R4" t="n">
-        <v>-215299000</v>
+        <v>-224064000</v>
       </c>
       <c r="S4" t="n">
-        <v>547996000</v>
+        <v>35722000</v>
       </c>
       <c r="T4" t="n">
-        <v>-763295000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>120000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>120000000</v>
-      </c>
+        <v>-259786000</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-957000</v>
+        <v>-356000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-957000</v>
+        <v>-510000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-291017000</v>
+        <v>365983000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-91830000</v>
+        <v>-172390000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2106509000</v>
+        <v>-414504000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2571424000</v>
+        <v>-366815000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2621751000</v>
+        <v>-1240460000</v>
       </c>
       <c r="AE4" t="n">
-        <v>524024000</v>
+        <v>116482000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-137707000</v>
+        <v>872340000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-436644000</v>
+        <v>-115177000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2073909000</v>
+        <v>2101961000</v>
       </c>
       <c r="AI4" t="n">
-        <v>56879000</v>
+        <v>-15359000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>221431000</v>
+        <v>-450106000</v>
       </c>
       <c r="AK4" t="n">
-        <v>15709000</v>
+        <v>21329000</v>
       </c>
       <c r="AL4" t="n">
-        <v>15709000</v>
+        <v>21329000</v>
       </c>
       <c r="AM4" t="n">
-        <v>213828000</v>
+        <v>1457471000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-9025000</v>
+        <v>3721000</v>
       </c>
       <c r="AO4" t="n">
-        <v>32000</v>
+        <v>-55521000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-5163849000</v>
+        <v>-2949175000</v>
       </c>
     </row>
   </sheetData>
@@ -3090,192 +3090,192 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Xiang Yang  Ding', 'age': 57, 'title': 'Chairman &amp; Administrative President', 'yearBorn': 1968, 'fiscalYear': 2023, 'totalPay': 735420, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhi Rong  Yan', 'age': 64, 'title': 'Executive Director', 'yearBorn': 1961, 'fiscalYear': 2023, 'totalPay': 365973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Juan  Lu', 'age': 48, 'title': 'Executive Director', 'yearBorn': 1977, 'fiscalYear': 2023, 'totalPay': 522322, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Judy  Cheung', 'title': 'Financial Controller', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Zhi Rong  Fang', 'age': 57, 'title': 'Head of Human Resources Department', 'yearBorn': 1968, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Fai  Leung Acca, C.P.A., Cpa Australia, Hkicpa', 'age': 60, 'title': 'Company Secretary', 'yearBorn': 1965, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Xiang Yang  Ding', 'age': 57, 'title': 'Chairman &amp; Administrative President', 'yearBorn': 1968, 'fiscalYear': 2023, 'totalPay': 735024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhi Rong  Yan', 'age': 64, 'title': 'Executive Director', 'yearBorn': 1961, 'fiscalYear': 2023, 'totalPay': 365776, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Juan  Lu', 'age': 48, 'title': 'Executive Director', 'yearBorn': 1977, 'fiscalYear': 2023, 'totalPay': 522041, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Judy  Cheung', 'title': 'Financial Controller', 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Zhi Rong  Fang', 'age': 57, 'title': 'Head of Human Resources Department', 'yearBorn': 1968, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Fai  Leung Acca, C.P.A., Cpa Australia, Hkicpa', 'age': 60, 'title': 'Company Secretary', 'yearBorn': 1965, 'fiscalYear': 2023, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.062</v>
+        <v>0.054</v>
       </c>
       <c r="AG2" t="n">
         <v>586403</v>
@@ -3505,7 +3505,7 @@
         <v>7792645623</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.53158706</v>
+        <v>-0.531305</v>
       </c>
       <c r="BK2" t="n">
         <v>1703980800</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.03</v>
@@ -3642,143 +3642,143 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CY2" t="n">
+      <c r="DA2" t="n">
         <v>1743407714</v>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>finmb_47235479</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="DF2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="inlineStr">
         <is>
           <t>GLORIOUS PPT H</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Glorious Property Holdings Limited</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1254447000000</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.01 - 0.01</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>0.01 - 0.01</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
         <v>1725026152</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DY2" t="n">
         <v>1725026152</v>
       </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
         <v>-0.43</v>
       </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.018811593</v>
-      </c>
-      <c r="DS2" t="n">
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.01882158</v>
+      </c>
+      <c r="EG2" t="n">
         <v>15</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1254447000000</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>0.01 - 0.01</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>0.01 - 0.01</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.01</v>
+      <c r="EI2" t="b">
+        <v>0</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
